--- a/airtable_json_uploader/json_files/Airtable - Ottima.xlsx
+++ b/airtable_json_uploader/json_files/Airtable - Ottima.xlsx
@@ -1352,9 +1352,11 @@
     <col customWidth="1" min="6" max="9" width="31.38"/>
     <col customWidth="1" min="10" max="11" width="28.75"/>
     <col customWidth="1" min="12" max="12" width="19.13"/>
-    <col customWidth="1" min="13" max="13" width="43.25"/>
-    <col customWidth="1" min="14" max="15" width="34.75"/>
-    <col customWidth="1" min="16" max="24" width="50.13"/>
+    <col customWidth="1" min="13" max="13" width="69.88"/>
+    <col customWidth="1" min="14" max="14" width="91.13"/>
+    <col customWidth="1" min="15" max="15" width="34.75"/>
+    <col customWidth="1" min="16" max="16" width="93.38"/>
+    <col customWidth="1" min="17" max="24" width="50.13"/>
     <col customWidth="1" min="25" max="25" width="18.88"/>
     <col customWidth="1" min="26" max="27" width="12.63"/>
   </cols>
